--- a/database/IT Actions Dimonekene.xlsx
+++ b/database/IT Actions Dimonekene.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\B.NIMI\Desktop\DIVERS\Emiles\storage\app\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\B.NIMI\Desktop\DIVERS\Emiles\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51901190-AA25-4B37-9966-3B20BE02F344}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DD6DF89-DAA9-4037-8C2B-1F8042F03528}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="5" activeTab="5" xr2:uid="{E9D5118C-A769-4C44-AF96-8C3A56EDA7ED}"/>
+    <workbookView xWindow="28690" yWindow="-110" windowWidth="29020" windowHeight="16420" firstSheet="5" activeTab="5" xr2:uid="{E9D5118C-A769-4C44-AF96-8C3A56EDA7ED}"/>
   </bookViews>
   <sheets>
     <sheet name="IT Action 28-02-22" sheetId="1" state="hidden" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="139">
   <si>
     <t>Aujourd'hui</t>
   </si>
@@ -966,6 +966,21 @@
      - Génération du Fichier Excel pour Mis à Jour dans POINTAGE_JOURNALIERS
      - Mis à jour des pointages coupe dans POINTAGE_JOURNALIERS
           </t>
+  </si>
+  <si>
+    <t>FD7</t>
+  </si>
+  <si>
+    <t>Pointage Manquant</t>
+  </si>
+  <si>
+    <t>-- Création interface ( Champs pour saisir : debut décade, Fin décade, Direction, Grade )
+ -- Récupération des pointages manquants par raport à une date : 
+ --     par Direction
+ --     par Grade
+-- Regroupement par 
+--   Date &gt; Employé
+--   Direction &gt; Employé &gt; Date</t>
   </si>
 </sst>
 </file>
@@ -2017,7 +2032,7 @@
       </c>
       <c r="D5" s="8">
         <f ca="1">TODAY()</f>
-        <v>46230</v>
+        <v>46245</v>
       </c>
       <c r="E5" s="9"/>
       <c r="F5" s="10"/>
@@ -2032,7 +2047,7 @@
       </c>
       <c r="D6" s="8">
         <f ca="1">TODAY()</f>
-        <v>46230</v>
+        <v>46245</v>
       </c>
       <c r="E6" s="9"/>
       <c r="F6" s="10"/>
@@ -2050,7 +2065,7 @@
       </c>
       <c r="D7" s="8">
         <f ca="1">TODAY()</f>
-        <v>46230</v>
+        <v>46245</v>
       </c>
       <c r="E7" s="9"/>
       <c r="F7" s="10"/>
@@ -8840,11 +8855,17 @@
       <c r="J7" s="64"/>
       <c r="K7" s="64"/>
     </row>
-    <row r="8" spans="1:11" s="65" customFormat="1" ht="14" x14ac:dyDescent="0.3">
-      <c r="A8" s="64"/>
-      <c r="B8" s="64"/>
+    <row r="8" spans="1:11" s="65" customFormat="1" ht="124" x14ac:dyDescent="0.3">
+      <c r="A8" s="67" t="s">
+        <v>136</v>
+      </c>
+      <c r="B8" s="66" t="s">
+        <v>137</v>
+      </c>
       <c r="C8" s="64"/>
-      <c r="D8" s="64"/>
+      <c r="D8" s="66" t="s">
+        <v>138</v>
+      </c>
       <c r="E8" s="64"/>
       <c r="F8" s="64"/>
       <c r="G8" s="64"/>
